--- a/Result/checksun_type/塑膠框.xlsx
+++ b/Result/checksun_type/塑膠框.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>69.42</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>69.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>70.06</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>69.31999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>70.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>1203.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>1436.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>1436.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1730.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1926.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1926.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-80.07901957981517</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>1203</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1203.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>68.97999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>69.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>70.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1814.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1436.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1436.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1763.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1912.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1912.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-53.78002400970604</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1814</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1814.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>68.46000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>69.41</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>70.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>70.18000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>882.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1583.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1583.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1848.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1980.9</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1980.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-79.7536009092039</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>882</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>882.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>68.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>69.42</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>70.27</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>70.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1859.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1710.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1710.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1929.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1984.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1984.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-14.15322501887204</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1859</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1859.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>69.08000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>69.41</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>70.39</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>70.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1424.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2070.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2070.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1854.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1970.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1970.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-24.61150142486667</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1424</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1424.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>69.42</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>69.47</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>70.52</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>70.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1203.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2024.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2024.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1789.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1949.3</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1949.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>7.934228760314681</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1203</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1203.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>70.04</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>69.47</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>70.67</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>70.67</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2551.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2091.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2091.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1806.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1986.2</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1986.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>77.82333514056268</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2551</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2551.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>70.34</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>69.45</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>70.78</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>69.45</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>70.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>1515.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2113.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>2113.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1644.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1966.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1966</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>30.45693942875391</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>1515</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1515.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>70.06</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>69.4</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>70.87</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70.87</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3661.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2148.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2148.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1557.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1970.74</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1970.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>72.70291200371435</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3661</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3661.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>69.52000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>69.23</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>70.92</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>70.92</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1192.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1639.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1639</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1219.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1949.24</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1949.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-99.47080260361759</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1192</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1192.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>69.44000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>69.13</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>69.13</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>71.01000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1537.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1553.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1553.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1303.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1962.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1962.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-77.34500909253393</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1537</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1537.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>13.32</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>13.83</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>14.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>14.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1213.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>527.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>527.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>585.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>567.68</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>567.6799999999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>21.00387133963898</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1213</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1213.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>13.37</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>14.48</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>206.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>340.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>340.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>497.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>555.26</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>555.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-46.08158973532466</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>206</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>206.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>13.43</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>14.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>272.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>332.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>332</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>647.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>577.06</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>577.0599999999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-32.37933449472541</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>272</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>272.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14.64</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>374.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>340.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>340.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>625.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>605.18</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>605.1799999999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-18.71970791905761</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>374</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>374.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>13.81</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>14.71</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>573.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>381.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>381</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>597.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>630.02</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>630.02</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-9.46596609956589</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>573</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>573.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.79</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>276.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>643.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>643.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>572.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>643.84</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>643.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-17.22969328245046</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>276</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>276.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>14.17</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>655.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>655.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>563.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>675.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>675</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>4.116042644944969</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>165</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>14.25</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>314.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>963.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>963</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>565.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>734.12</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>734.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>46.35580673247603</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>314</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>314.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>14.22</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>14.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15.03</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>911.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>911.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>580.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>762.26</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>762.26</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>89.0784766170749</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>577</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>577.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,21 +9657,17 @@
           <t>14.13</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>14.03</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AM22" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AO22" t="inlineStr">
         <is>
           <t>15.11</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>15.11</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>40.16</t>
@@ -9832,20 +9708,16 @@
           <t>1887.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>813.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>813.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>561.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>794.04</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>794.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>118.7509165730348</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1887</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1887.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>13.95</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>15.19</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.19</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>333.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>500.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>500.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>432.9</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>783.6</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>783.6</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>16.54186948965486</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>333</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>333.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>10.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>10.85</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6305887.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7393258.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7393258.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>10517267.3</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>20568071.26</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>20568071.26</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1787012.246778358</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6305887</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6305887.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>10.21</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>11.22</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>11.22</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>6730463.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>8143750.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>8143750.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>10751948.6</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>20786752.56</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>20786752.56</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1731711.459589692</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>6730463</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>6730463.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>10.18</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>10.96</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>11.24</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>11.24</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>8188113.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>10252271.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>10252271.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>11380459.0</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>21012264.76</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>21012264.76</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1636353.782906249</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>8188113</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>8188113.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>10.27</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>11.03</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>11.26</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11.26</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>9675415.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>12157509.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>12157509.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11738500.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>21280071.54</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>21280071.54</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1597864.109683253</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>9675415</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>9675415.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>10.43</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>11.28</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>11.28</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>6066413.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>12520435.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>12520435.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11198491.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>21364951.88</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>21364951.88</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1645166.072590286</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>6066413</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>6066413.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>10.65</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>11.17</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>11.3</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>10058347.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>13641276.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>13641276.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11429840.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>21624569.6</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>21624569.6</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1267305.588436393</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>10058347</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>10058347.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>11.25</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>11.32</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>17273069.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>13360147.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>13360147</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11469505.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>21758890.56</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>21758890.56</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1109951.197200963</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>17273069</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>17273069.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>10.98</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>11.32</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>17714305.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>12508646.6</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>12508646.6</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>10959217.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>21599596.86</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>21599596.86</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1618524.024107456</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>17714305</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>17714305.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>11.09</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>11.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>11490043.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>11319491.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>11319491.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>10877105.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21406229.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21406229.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-2334527.490255751</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>11490043</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>11490043.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>11.14</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>11.46</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>11670618.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>9876547.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>9876547.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>11219565.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21593346.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21593346.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2607128.38867275</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>11670618</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>11670618.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>11.16</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>11.51</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>11.34</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>11.34</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>8652700.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>9218405.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>9218405</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>12205749.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21688059.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21688059.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-2922793.836815866</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>8652700</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>8652700.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>83.88</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>77.41</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>77.41</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>213896698.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>504772584.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>504772584.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>332966839.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>296796978.54</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>296796978.54</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>8142708.803127825</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>213896698</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>213896698.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>83.22</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>81.35</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>77.18</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>77.18000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>333409921.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>480880190.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>480880190.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>371960417.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>294937049.8</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>294937049.8</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>26184662.6555354</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>333409921</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>333409921.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>82.82</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>81.28</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>77.03</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>81.28</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>77.03</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>573541931.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>439505475.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>439505475.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>355695238.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>291760727.28</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>291760727.28</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>38218727.74270576</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>573541931</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>573541931.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>82.28</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>81.06</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>76.84</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>76.84</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>818618845.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>368965626.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>368965626.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>310112139.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>284161203.66</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>284161203.66</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>28316865.09070969</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>818618845</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>818618845.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>81.08</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>80.78</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>76.66</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>76.66</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>584395526.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>236650302.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>236650302.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>239077486.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>271483731.38</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>271483731.38</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-13098210.37966722</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>584395526</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>584395526.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>79.84</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>80.47</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>76.38</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>76.38</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>94434729.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>161161094.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>161161094</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>202232241.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>261484234.4</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>261484234.4</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-46699455.07378897</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>94434729</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>94434729.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>80.32</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>80.35</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>76.25</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>76.25</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>126536347.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>263040645.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>263040645.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>216492202.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>262852891.7</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>262852891.7</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-40537595.84847045</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>126536347</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>126536347.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>79.9</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>80.24</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>76.19</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>80.23999999999999</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>76.19</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>220842684.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>271885001.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>271885001.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>223066373.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>263858802.06</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>263858802.06</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-33726627.60342717</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>220842684</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>220842684.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>79.35999999999999</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>79.92</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>76.05</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>76.05</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>157042227.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>251258651.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>251258651.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>223487178.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>263437077.76</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>263437077.76</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-32896400.94610006</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>157042227</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>157042227.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>79.32000000000001</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>79.76</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>76.01</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>76.01000000000001</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>206949483.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>241504669.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>241504669.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>250238152.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>268014618.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>268014618.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-23699728.15184349</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>206949483</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>206949483.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>79.26</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>79.28</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>75.98</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>75.98</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>603832486.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>243303388.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>243303388.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>478474465.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>273726863.86</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>273726863.86</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-15062411.29748261</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>603832486</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>603832486.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>32.36</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>33.57</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>33.57</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>403535423.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>568945866.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>568945866.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>551325175.1</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>652100733.04</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>652100733.04</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-64629376.5640012</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>403535423</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>403535423.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>32.41</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>33.75</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>36.78</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>36.78</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>363440217.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>575528949.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>575528949.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>594264436.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>657290966.96</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>657290966.96</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-58722927.5542357</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>363440217</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>363440217.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>32.3</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>33.94</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>36.93</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>36.93</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>451484020.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>575978704.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>575978704.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>641378457.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>656768454.26</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>656768454.26</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-43891980.91334808</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>451484020</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>451484020.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>32.09</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>34.14</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>37.07</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>34.14</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>37.07</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>569640781.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>620997783.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>620997783.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>705807978.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>655783883.94</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>655783883.9400001</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-30570608.14374614</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>569640781</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>569640781.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>32.14</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>34.4</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>37.2</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>1056628890.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>631631786.8</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>631631786.8</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>709807982.0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>651233510.34</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>651233510.34</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-23107921.14632392</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>1056628890</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>1056628890.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>32.12</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>34.62</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>436450840.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>533704484.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>533704484</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>667262298.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>638216857.76</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>638216857.76</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-63798954.21620893</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>436450840</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>436450840.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>34.95</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>37.46</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>37.46</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>365688993.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>612999923.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>612999923.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>705359369.1</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>635887126.76</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>635887126.76</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-53202819.16546595</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>365688993</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>365688993.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>32.81</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>35.28</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>37.61</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>37.61</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>676579414.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>706778210.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>706778210.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>768838281.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>633235828.68</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>633235828.6799999</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-28583756.22992349</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>676579414</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>676579414.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>33.39</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>35.56</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>37.76</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>622810797.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>790618174.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>790618174</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>763691422.1</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>627286041.56</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>627286041.5599999</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-25702505.84950864</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>622810797</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>622810797.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>34.07</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>35.84</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>566992376.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>787984177.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>787984177.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>817890552.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>622376486.36</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>622376486.36</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-14907563.99000478</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>566992376</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>566992376.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>34.47</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>832928036.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>800820113.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>800820113.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>848956198.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>625070436.22</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>625070436.22</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>7026739.630357981</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>832928036</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>832928036.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>15.77</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>16.9</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>2276.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>2276.4</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>2169.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2929.94</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2929.94</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>68.27476452672317</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1612</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1612.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>15.86</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>16.93</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>5816.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>2135.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>2135.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>2406.3</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2973.86</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2973.86</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>155.8338220959245</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>5816</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>5816.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>15.96</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>16.96</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>16.96</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>796.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1325.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1325</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1925.8</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2912.66</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2912.66</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-175.0758750229279</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>796</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>796.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>16.01</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>16.46</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>2223.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>2207.8</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>2207.8</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1969.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2984.7</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2984.7</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-103.6941610847555</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>2223</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>2223.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>16.12</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>16.53</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>935.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>2025.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>2025</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1934.8</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>3006.12</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>3006.12</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-150.9097782771964</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>935</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>935.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>16.2</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>17.04</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>908.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>2062.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>2062.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1981.4</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>3040.84</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>3040.84</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-74.9710250422122</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>908</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>908.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>16.29</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1763.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>2677.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>2677</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>2141.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>3096.62</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>3096.62</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>39.08330190213019</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1763</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1763.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>16.39</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>16.71</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>17.1</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>5210.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2526.6</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2526.6</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2151.2</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>3177.52</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>3177.52</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>109.0150796118287</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>5210</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>5210.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>16.5</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>16.76</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>17.12</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>17.12</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1309.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1730.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1730.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1853.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>3144.96</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>3144.96</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-164.297205074738</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1309</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1309.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>16.49</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>16.79</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>17.13</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1124.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1844.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1844.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1896.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>3192.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>3192.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-130.9112830171648</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1124</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1124.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>16.47</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>17.16</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>17.16</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3979.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1900.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1900</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>1928.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>3243.68</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>3243.68</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-58.72027711287592</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3979</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3979.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
